--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,1746 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126030305</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>504</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>543592</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6999597</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Detalj: 12 skott, varav 9 blommande och 3 vegetativa. Fuktig skog nära bäck.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126030335</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>504</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543764</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6999706</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Detalj: 11 skott, varav 8 blommande och 3 vegetativa. Hyggeskant/sumpskog. Överblommade, 3 små grupper.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126030306</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>504</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543589</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6999597</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Fuktig skog nära bäck.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126030325</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>504</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543765</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6999632</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126030327</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>504</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>543756</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6999707</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Detalj: 5 skott, varav 3 blommande och 2 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126030338</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>504</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>543763</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6999705</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Detalj: 10 skott, varav 6 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126030328</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>504</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543761</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6999708</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Detalj: 2 skott, varav 2 blommande Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126030307</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>504</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>543588</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6999592</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Detalj: 6 skott, varav  blommande och 6 vegetativa. Fuktig skog nära bäck.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126030340</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>504</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>543759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6999698</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126030336</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>504</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>543761</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6999707</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Detalj: 12 skott, varav 5 blommande och 7 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126030333</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>504</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>543764</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6999700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Detalj: 31 skott, varav 21 blommande och 10 vegetativa. Hyggeskant/sumpskog. Överblommade. 1 stor och 3 små grupper.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126030339</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>504</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>543763</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6999703</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Detalj: 22 skott, varav 5 blommande och 17 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126030309</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>504</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>543585</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6999594</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Detalj: 9 skott, varav 1 blommande och 8 vegetativa. Fuktig skog nära bäck.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126030324</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>504</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>543758</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6999620</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126030342</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>504</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>543758</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6999701</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,7 +809,7 @@
         <v>126030305</v>
       </c>
       <c r="B3" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126030335</v>
+        <v>126030306</v>
       </c>
       <c r="B4" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543764</v>
+        <v>543589</v>
       </c>
       <c r="R4" t="n">
-        <v>6999706</v>
+        <v>6999597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Detalj: 11 skott, varav 8 blommande och 3 vegetativa. Hyggeskant/sumpskog. Överblommade, 3 små grupper.</t>
+          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126030306</v>
+        <v>126030325</v>
       </c>
       <c r="B5" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543589</v>
+        <v>543765</v>
       </c>
       <c r="R5" t="n">
-        <v>6999597</v>
+        <v>6999632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126030325</v>
+        <v>126030327</v>
       </c>
       <c r="B6" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543765</v>
+        <v>543756</v>
       </c>
       <c r="R6" t="n">
-        <v>6999632</v>
+        <v>6999707</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
+          <t>Detalj: 5 skott, varav 3 blommande och 2 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126030327</v>
+        <v>126030338</v>
       </c>
       <c r="B7" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543756</v>
+        <v>543763</v>
       </c>
       <c r="R7" t="n">
-        <v>6999707</v>
+        <v>6999705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Detalj: 5 skott, varav 3 blommande och 2 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 10 skott, varav 6 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126030338</v>
+        <v>126030328</v>
       </c>
       <c r="B8" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543763</v>
+        <v>543761</v>
       </c>
       <c r="R8" t="n">
-        <v>6999705</v>
+        <v>6999708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 10 skott, varav 6 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 2 skott, varav 2 blommande Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126030328</v>
+        <v>126030307</v>
       </c>
       <c r="B9" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543761</v>
+        <v>543588</v>
       </c>
       <c r="R9" t="n">
-        <v>6999708</v>
+        <v>6999592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 2 skott, varav 2 blommande Hyggeskant/sumpskog.</t>
+          <t>Detalj: 6 skott, varav  blommande och 6 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126030307</v>
+        <v>126030340</v>
       </c>
       <c r="B10" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543588</v>
+        <v>543759</v>
       </c>
       <c r="R10" t="n">
-        <v>6999592</v>
+        <v>6999698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Detalj: 6 skott, varav  blommande och 6 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126030340</v>
+        <v>126030336</v>
       </c>
       <c r="B11" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543759</v>
+        <v>543761</v>
       </c>
       <c r="R11" t="n">
-        <v>6999698</v>
+        <v>6999707</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 12 skott, varav 5 blommande och 7 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126030336</v>
+        <v>126030333</v>
       </c>
       <c r="B12" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543761</v>
+        <v>543764</v>
       </c>
       <c r="R12" t="n">
-        <v>6999707</v>
+        <v>6999700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Detalj: 12 skott, varav 5 blommande och 7 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 31 skott, varav 21 blommande och 10 vegetativa. Hyggeskant/sumpskog. Överblommade. 1 stor och 3 små grupper.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126030333</v>
+        <v>126030339</v>
       </c>
       <c r="B13" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543764</v>
+        <v>543763</v>
       </c>
       <c r="R13" t="n">
-        <v>6999700</v>
+        <v>6999703</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Detalj: 31 skott, varav 21 blommande och 10 vegetativa. Hyggeskant/sumpskog. Överblommade. 1 stor och 3 små grupper.</t>
+          <t>Detalj: 22 skott, varav 5 blommande och 17 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126030339</v>
+        <v>126030309</v>
       </c>
       <c r="B14" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543763</v>
+        <v>543585</v>
       </c>
       <c r="R14" t="n">
-        <v>6999703</v>
+        <v>6999594</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Detalj: 22 skott, varav 5 blommande och 17 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 9 skott, varav 1 blommande och 8 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126030309</v>
+        <v>126030324</v>
       </c>
       <c r="B15" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543585</v>
+        <v>543758</v>
       </c>
       <c r="R15" t="n">
-        <v>6999594</v>
+        <v>6999620</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Detalj: 9 skott, varav 1 blommande och 8 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126030324</v>
+        <v>126030342</v>
       </c>
       <c r="B16" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2366,7 +2366,7 @@
         <v>543758</v>
       </c>
       <c r="R16" t="n">
-        <v>6999620</v>
+        <v>6999701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
+          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,122 +2427,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>126030342</v>
-      </c>
-      <c r="B17" t="n">
-        <v>98238</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>504</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Cypripedium calceolus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Motjärnarna / SV /, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>543758</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6999701</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Stugun</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,7 +809,7 @@
         <v>126030305</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126030306</v>
+        <v>126030335</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543589</v>
+        <v>543764</v>
       </c>
       <c r="R4" t="n">
-        <v>6999597</v>
+        <v>6999706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 11 skott, varav 8 blommande och 3 vegetativa. Hyggeskant/sumpskog. Överblommade, 3 små grupper.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126030325</v>
+        <v>126030306</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543765</v>
+        <v>543589</v>
       </c>
       <c r="R5" t="n">
-        <v>6999632</v>
+        <v>6999597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
+          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126030327</v>
+        <v>126030325</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543756</v>
+        <v>543765</v>
       </c>
       <c r="R6" t="n">
-        <v>6999707</v>
+        <v>6999632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Detalj: 5 skott, varav 3 blommande och 2 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126030338</v>
+        <v>126030327</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543763</v>
+        <v>543756</v>
       </c>
       <c r="R7" t="n">
-        <v>6999705</v>
+        <v>6999707</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Detalj: 10 skott, varav 6 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 5 skott, varav 3 blommande och 2 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126030328</v>
+        <v>126030338</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543761</v>
+        <v>543763</v>
       </c>
       <c r="R8" t="n">
-        <v>6999708</v>
+        <v>6999705</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 2 skott, varav 2 blommande Hyggeskant/sumpskog.</t>
+          <t>Detalj: 10 skott, varav 6 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126030307</v>
+        <v>126030328</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543588</v>
+        <v>543761</v>
       </c>
       <c r="R9" t="n">
-        <v>6999592</v>
+        <v>6999708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 6 skott, varav  blommande och 6 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 2 skott, varav 2 blommande Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126030340</v>
+        <v>126030307</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543759</v>
+        <v>543588</v>
       </c>
       <c r="R10" t="n">
-        <v>6999698</v>
+        <v>6999592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 6 skott, varav  blommande och 6 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126030336</v>
+        <v>126030340</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543761</v>
+        <v>543759</v>
       </c>
       <c r="R11" t="n">
-        <v>6999707</v>
+        <v>6999698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Detalj: 12 skott, varav 5 blommande och 7 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126030333</v>
+        <v>126030336</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543764</v>
+        <v>543761</v>
       </c>
       <c r="R12" t="n">
-        <v>6999700</v>
+        <v>6999706</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Detalj: 31 skott, varav 21 blommande och 10 vegetativa. Hyggeskant/sumpskog. Överblommade. 1 stor och 3 små grupper.</t>
+          <t>Detalj: 12 skott, varav 5 blommande och 7 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126030339</v>
+        <v>126030333</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543763</v>
+        <v>543764</v>
       </c>
       <c r="R13" t="n">
-        <v>6999703</v>
+        <v>6999700</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Detalj: 22 skott, varav 5 blommande och 17 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 31 skott, varav 21 blommande och 10 vegetativa. Hyggeskant/sumpskog. Överblommade. 1 stor och 3 små grupper.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126030309</v>
+        <v>126030339</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543585</v>
+        <v>543763</v>
       </c>
       <c r="R14" t="n">
-        <v>6999594</v>
+        <v>6999703</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Detalj: 9 skott, varav 1 blommande och 8 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 22 skott, varav 5 blommande och 17 vegetativa. Hyggeskant/sumpskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126030324</v>
+        <v>126030309</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543758</v>
+        <v>543585</v>
       </c>
       <c r="R15" t="n">
-        <v>6999620</v>
+        <v>6999594</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
+          <t>Detalj: 9 skott, varav 1 blommande och 8 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126030342</v>
+        <v>126030324</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2366,7 +2366,7 @@
         <v>543758</v>
       </c>
       <c r="R16" t="n">
-        <v>6999701</v>
+        <v>6999620</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,6 +2427,122 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126030342</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98244</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>504</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>543758</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6999701</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Detalj: 14 skott, varav 10 blommande och 4 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,853 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129563687</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98630</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>504</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>543758</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6999700</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Detalj: 16 skott, varav 11 blommande och 5 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129563677</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98630</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>504</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543765</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6999632</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Fuktig skog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129563680</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98630</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>504</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543761</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6999708</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Detalj: 45 skott, varav 31 blommande och 14 vegetativa. Hyggeskant/sumpskog. 7 grupper.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129563675</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98630</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>504</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543758</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6999620</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Fuktig skog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129563683</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98630</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>504</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>543764</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6999700</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Detalj: 31 skott, varav 21 överblommade/blommande och 10 vegetativa. Hyggeskant/sumpskog. 1 stor och 3 små grupper.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129563685</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98630</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>504</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>543763</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6999706</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129563671</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98630</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>504</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543588</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6999594</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Fuktig skog, nära bäck</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -1411,7 +1411,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129563685</v>
+        <v>129563671</v>
       </c>
       <c r="B8" t="n">
         <v>98633</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543763</v>
+        <v>543588</v>
       </c>
       <c r="R8" t="n">
-        <v>6999706</v>
+        <v>6999594</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129563671</v>
+        <v>129563685</v>
       </c>
       <c r="B9" t="n">
         <v>98633</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543588</v>
+        <v>543763</v>
       </c>
       <c r="R9" t="n">
-        <v>6999594</v>
+        <v>6999706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktig skog, nära bäck</t>
+          <t>Hyggeskant/sumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -1411,7 +1411,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129563671</v>
+        <v>129563685</v>
       </c>
       <c r="B8" t="n">
         <v>98633</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543588</v>
+        <v>543763</v>
       </c>
       <c r="R8" t="n">
-        <v>6999594</v>
+        <v>6999706</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Fuktig skog, nära bäck</t>
+          <t>Hyggeskant/sumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129563685</v>
+        <v>129563671</v>
       </c>
       <c r="B9" t="n">
         <v>98633</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543763</v>
+        <v>543588</v>
       </c>
       <c r="R9" t="n">
-        <v>6999706</v>
+        <v>6999594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98662</v>
+        <v>98674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98662</v>
+        <v>98674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98662</v>
+        <v>98674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98662</v>
+        <v>98674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98662</v>
+        <v>98674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129563685</v>
+        <v>129563671</v>
       </c>
       <c r="B8" t="n">
-        <v>98662</v>
+        <v>98674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543763</v>
+        <v>543588</v>
       </c>
       <c r="R8" t="n">
-        <v>6999706</v>
+        <v>6999594</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129563671</v>
+        <v>129563685</v>
       </c>
       <c r="B9" t="n">
-        <v>98662</v>
+        <v>98674</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543588</v>
+        <v>543763</v>
       </c>
       <c r="R9" t="n">
-        <v>6999594</v>
+        <v>6999706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktig skog, nära bäck</t>
+          <t>Hyggeskant/sumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129563671</v>
+        <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543588</v>
+        <v>543763</v>
       </c>
       <c r="R8" t="n">
-        <v>6999594</v>
+        <v>6999706</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Fuktig skog, nära bäck</t>
+          <t>Hyggeskant/sumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129563685</v>
+        <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543763</v>
+        <v>543588</v>
       </c>
       <c r="R9" t="n">
-        <v>6999706</v>
+        <v>6999594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -1411,7 +1411,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129563685</v>
+        <v>129563671</v>
       </c>
       <c r="B8" t="n">
         <v>98675</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543763</v>
+        <v>543588</v>
       </c>
       <c r="R8" t="n">
-        <v>6999706</v>
+        <v>6999594</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129563671</v>
+        <v>129563685</v>
       </c>
       <c r="B9" t="n">
         <v>98675</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543588</v>
+        <v>543763</v>
       </c>
       <c r="R9" t="n">
-        <v>6999594</v>
+        <v>6999706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktig skog, nära bäck</t>
+          <t>Hyggeskant/sumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129563671</v>
+        <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543588</v>
+        <v>543763</v>
       </c>
       <c r="R8" t="n">
-        <v>6999594</v>
+        <v>6999706</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Fuktig skog, nära bäck</t>
+          <t>Hyggeskant/sumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129563685</v>
+        <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543763</v>
+        <v>543588</v>
       </c>
       <c r="R9" t="n">
-        <v>6999706</v>
+        <v>6999594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>129563687</v>
       </c>
       <c r="B3" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129563677</v>
       </c>
       <c r="B4" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>129563680</v>
       </c>
       <c r="B5" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129563675</v>
       </c>
       <c r="B6" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129563683</v>
       </c>
       <c r="B7" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>129563685</v>
       </c>
       <c r="B8" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>129563671</v>
       </c>
       <c r="B9" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68299257</v>
+        <v>62022980</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,31 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Motjärnarna / SV /, Jmt</t>
+          <t>Motjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543758.6585300008</v>
+        <v>543759</v>
       </c>
       <c r="R2" t="n">
-        <v>6999695.714606421</v>
+        <v>6999696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Detalj: 59 skott, varav 34 blommande och 25 vegetativa.</t>
+          <t>2016-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,26 +756,39 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gransumpskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2 substratenheter</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Persson, Arne Lysell</t>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129563687</v>
+        <v>68299258</v>
       </c>
       <c r="B3" t="n">
-        <v>98700</v>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543758</v>
+        <v>543587</v>
       </c>
       <c r="R3" t="n">
-        <v>6999700</v>
+        <v>6999570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,17 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Detalj: 16 skott, varav 11 blommande och 5 vegetativa. Hyggeskant/sumpskog.</t>
+          <t>Detalj: 113 skott, varav 67 blommande och 46 vegetativa.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,11 +885,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hyggeskant/sumpskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -920,17 +894,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Lennart Persson, Arne Lysell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129563677</v>
+        <v>129563671</v>
       </c>
       <c r="B4" t="n">
-        <v>98700</v>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543765</v>
+        <v>543588</v>
       </c>
       <c r="R4" t="n">
-        <v>6999632</v>
+        <v>6999594</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
+          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1004,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Fuktig skog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129563680</v>
+        <v>129563672</v>
       </c>
       <c r="B5" t="n">
-        <v>98700</v>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1052,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543761</v>
+        <v>543584</v>
       </c>
       <c r="R5" t="n">
-        <v>6999708</v>
+        <v>6999583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1111,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Detalj: 45 skott, varav 31 blommande och 14 vegetativa. Hyggeskant/sumpskog. 7 grupper.</t>
+          <t>Detalj: 54 skott, varav 24 blommande och 30 vegetativa. Fuktig skog nära bäck.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1125,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1169,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129563675</v>
+        <v>129563673</v>
       </c>
       <c r="B6" t="n">
-        <v>98700</v>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1173,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1218,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543758</v>
+        <v>543582</v>
       </c>
       <c r="R6" t="n">
-        <v>6999620</v>
+        <v>6999569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1232,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
+          <t>Detalj: 90 skott, varav 36 blommande och 54 vegetativa. Fuktig skog nära bäck. 4 grupper och några spridda.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,7 +1246,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Fuktig skog</t>
+          <t>Fuktig skog, nära bäck</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1290,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129563683</v>
+        <v>129563674</v>
       </c>
       <c r="B7" t="n">
-        <v>98700</v>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1294,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1330,7 +1304,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1339,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543764</v>
+        <v>543586</v>
       </c>
       <c r="R7" t="n">
-        <v>6999700</v>
+        <v>6999564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1353,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Detalj: 31 skott, varav 21 överblommade/blommande och 10 vegetativa. Hyggeskant/sumpskog. 1 stor och 3 små grupper.</t>
+          <t>Detalj: 20 skott, alla vegetativa. Fuktig skog. 4 grupper.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,7 +1367,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1411,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129563685</v>
+        <v>129563675</v>
       </c>
       <c r="B8" t="n">
-        <v>98700</v>
+        <v>99024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1415,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543763</v>
+        <v>543758</v>
       </c>
       <c r="R8" t="n">
-        <v>6999706</v>
+        <v>6999620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1474,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+          <t>Detalj: 2 skott, varav 1 blommande och 1 vegetativ. Fuktig skog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1488,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hyggeskant/sumpskog</t>
+          <t>Fuktig skog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129563671</v>
+        <v>129563677</v>
       </c>
       <c r="B9" t="n">
-        <v>98700</v>
+        <v>99024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543588</v>
+        <v>543765</v>
       </c>
       <c r="R9" t="n">
-        <v>6999594</v>
+        <v>6999632</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1595,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Detalj: 41 skott, varav 20 blommande och 21 vegetativa. Fuktig skog nära bäck.</t>
+          <t>Detalj: 41 skott, varav 21 blommande och 20 vegetativa. Fuktig skog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1609,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktig skog, nära bäck</t>
+          <t>Fuktig skog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1650,6 +1624,490 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129563680</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99024</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>504</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>543761</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6999708</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Detalj: 45 skott, varav 31 blommande och 14 vegetativa. Hyggeskant/sumpskog. 7 grupper.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129563683</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99024</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>504</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>543764</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6999700</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Detalj: 31 skott, varav 21 överblommade/blommande och 10 vegetativa. Hyggeskant/sumpskog. 1 stor och 3 små grupper.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129563685</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99024</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>504</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>543763</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6999706</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Detalj: 81 skott, varav 43 överblommade/blommande och 38 vegetativa. Hyggeskant/sumpskog. 8 grupper.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129563687</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99024</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>504</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Motjärnarna / SV /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>543758</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6999700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Detalj: 16 skott, varav 11 blommande och 5 vegetativa. Hyggeskant/sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hyggeskant/sumpskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23930-2024 artfynd.xlsx
+++ b/artfynd/A 23930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62022980</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68299258</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563671</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563672</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563673</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563674</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1503,6 +1538,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1624,6 +1664,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563677</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1745,6 +1790,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563680</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1866,6 +1916,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563683</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1987,6 +2042,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563685</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2108,8 +2168,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563687</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>